--- a/tools/pet-grooming-receipt-form/包月客戶簽收單.xlsx
+++ b/tools/pet-grooming-receipt-form/包月客戶簽收單.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -522,7 +522,7 @@
           <t>日期：______ 年 ____ 月 ____ 日</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>美容師：________________      （此單用途：包月客戶 / 新購 + 次數扣抵）</t>
         </is>
@@ -542,41 +542,36 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>客戶姓名</t>
+          <t>寵物名</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>寵物名</t>
+          <t>服務項目（勾選）</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>服務項目（勾選）</t>
+          <t>本次狀態（勾選）</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>本次狀態（勾選）</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>金額
 (NT$)</t>
         </is>
       </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>付款方式（勾選）</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>付款方式（勾選）</t>
+          <t>簽收</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>簽收</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -588,25 +583,24 @@
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="27.8" customHeight="1">
       <c r="A5" s="7" t="n">
@@ -614,25 +608,24 @@
       </c>
       <c r="B5" s="8" t="inlineStr"/>
       <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6" ht="27.8" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -640,25 +633,24 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="27.8" customHeight="1">
       <c r="A7" s="7" t="n">
@@ -666,25 +658,24 @@
       </c>
       <c r="B7" s="8" t="inlineStr"/>
       <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="27.8" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -692,25 +683,24 @@
       </c>
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="27.8" customHeight="1">
       <c r="A9" s="7" t="n">
@@ -718,25 +708,24 @@
       </c>
       <c r="B9" s="8" t="inlineStr"/>
       <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10" ht="27.8" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -744,25 +733,24 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="27.8" customHeight="1">
       <c r="A11" s="7" t="n">
@@ -770,25 +758,24 @@
       </c>
       <c r="B11" s="8" t="inlineStr"/>
       <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="27.8" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -796,25 +783,24 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="27.8" customHeight="1">
       <c r="A13" s="7" t="n">
@@ -822,25 +808,24 @@
       </c>
       <c r="B13" s="8" t="inlineStr"/>
       <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
     </row>
     <row r="14" ht="27.8" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -848,25 +833,24 @@
       </c>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="27.8" customHeight="1">
       <c r="A15" s="7" t="n">
@@ -874,25 +858,24 @@
       </c>
       <c r="B15" s="8" t="inlineStr"/>
       <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
       <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr"/>
     </row>
     <row r="16" ht="27.8" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -900,25 +883,24 @@
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="27.8" customHeight="1">
       <c r="A17" s="7" t="n">
@@ -926,25 +908,24 @@
       </c>
       <c r="B17" s="8" t="inlineStr"/>
       <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr"/>
       <c r="I17" s="8" t="inlineStr"/>
-      <c r="J17" s="8" t="inlineStr"/>
     </row>
     <row r="18" ht="27.8" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -952,25 +933,24 @@
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>☐洗澡  ☐全美容  ☐剪指甲  ☐SPA  ☐其他___</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>☐新購  ☐第___次</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>☐現金 ☐匯款 ☐LINE Pay</t>
-        </is>
-      </c>
+          <t>☐新購  ☐第___次</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>☐現金 ☐匯款 ☐LINE Pay</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -982,10 +962,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
